--- a/healthcare_forms/035_required_screening_questions--healthcare_forms.xlsx
+++ b/healthcare_forms/035_required_screening_questions--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>What is your medical history?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Temperature Check</t>
+          <t>What is your current temperature?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Symptoms</t>
+          <t>What symptoms do you currently experience?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_info_1</t>
+          <t>patient_info_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>What is your contact information?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Do you have any known medical conditions?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Symptoms</t>
+          <t>How do you describe your current symptoms?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>contact_info_2</t>
+          <t>patient_info_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>What is your phone number?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,412 +676,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>medical_history_3</t>
+          <t>test_results_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>When were your test results available?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>symptoms_3</t>
+          <t>test_results_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Symptoms</t>
+          <t>What are your test results?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_info_3</t>
+          <t>test_results_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>Test Results 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>medical_history_4</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>symptoms_4</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Symptoms</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>contact_info_4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>medical_history_5</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>symptoms_5</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Symptoms</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>contact_info_5</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Contact Info</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>test_results_1</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Test Results</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>test_results_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Test Results</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>test_results_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Test Results</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>test_results_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Test Results</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>test_results_5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Test Results</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>test_results_6</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Test Results</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>test_results_7</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Test Results</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>test_results_8</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Test Results</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>test_results_9</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Test Results</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1205,142 +860,6 @@
       <c r="C6" t="inlineStr">
         <is>
           <t>Fatigue</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>symptoms_3_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>rash</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Rash</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>symptoms_3_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>runny_nose</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Runny Nose</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>symptoms_3_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>coughing</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Coughing</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>symptoms_4_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>confusion</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Confusion</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>symptoms_4_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>muscle_aches</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Muscle Aches</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>symptoms_4_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>diarrhea</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Diarrhea</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>symptoms_5_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>confusion</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Confusion</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>symptoms_5_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>muscle_aches</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Muscle Aches</t>
         </is>
       </c>
     </row>
